--- a/Doc/作業メモspring Itsシステム.xlsx
+++ b/Doc/作業メモspring Itsシステム.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbbb\Documents\LearningSpringIts\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B01F85-CAA9-4E6F-91F5-8C78EDCB15AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CF02A4-2A65-4588-B4E1-2B1AAD710C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14925" yWindow="0" windowWidth="13980" windowHeight="15585" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="環境構築あれこれ" sheetId="3" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="90">
   <si>
     <t>作業者</t>
     <rPh sb="0" eb="3">
@@ -817,6 +817,46 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>12. サービス層を作ってビジネスロジックを分離しよう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>serviceに処理を移動して、controllerは呼び出すだけ</t>
+    <rPh sb="8" eb="10">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>13. Dependency Injection とは</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14. Dependency Injection を使おう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15. H2データベースとMyBatisのセットアップをしよう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16. schema.sql と data.sql でテーブル作成と初期データ投入をしよう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>18. データアクセス層を作ってデータベースにselect文を実行しよう</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -1052,14 +1092,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2524,7 +2564,7 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -2560,6 +2600,182 @@
         <a:xfrm>
           <a:off x="1387929" y="7143750"/>
           <a:ext cx="8640000" cy="4860000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>581</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>473463</xdr:colOff>
+      <xdr:row>586</xdr:row>
+      <xdr:rowOff>92089</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{949D953F-E317-BD75-1856-E2EED592F85F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1391478" y="7769087"/>
+          <a:ext cx="6735115" cy="1086002"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>588</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>397252</xdr:colOff>
+      <xdr:row>600</xdr:row>
+      <xdr:rowOff>120033</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAC3EE0B-B02B-7571-BA64-705A4AD9D9D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1391478" y="9160565"/>
+          <a:ext cx="6658904" cy="2505425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>614</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>197833</xdr:colOff>
+      <xdr:row>629</xdr:row>
+      <xdr:rowOff>190529</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="図 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32709260-9B55-C362-9003-9FF70301F06B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1391478" y="14328913"/>
+          <a:ext cx="5068007" cy="3172268"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>632</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>597305</xdr:colOff>
+      <xdr:row>648</xdr:row>
+      <xdr:rowOff>39377</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{100B860D-F66F-8BAE-992B-CF80EA30EFEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1391478" y="17907000"/>
+          <a:ext cx="6858957" cy="3219899"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2845,19 +3061,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="16.5" thickBot="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5848,7 +6064,7 @@
     <row r="188" spans="2:15">
       <c r="B188" s="7"/>
       <c r="C188" s="14"/>
-      <c r="D188" s="19" t="s">
+      <c r="D188" s="17" t="s">
         <v>70</v>
       </c>
       <c r="E188" s="8"/>
@@ -5866,7 +6082,7 @@
     <row r="189" spans="2:15">
       <c r="B189" s="7"/>
       <c r="C189" s="14"/>
-      <c r="D189" s="19" t="s">
+      <c r="D189" s="17" t="s">
         <v>71</v>
       </c>
       <c r="E189" s="8"/>
@@ -7538,19 +7754,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="16.5" thickBot="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13013,19 +13229,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="16.5" thickBot="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15818,19 +16034,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="16.5" thickBot="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16316,19 +16532,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="16.5" thickBot="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
@@ -24975,7 +25191,7 @@
     </row>
     <row r="541" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B541" s="7"/>
-      <c r="C541" s="20" t="s">
+      <c r="C541" s="18" t="s">
         <v>77</v>
       </c>
       <c r="D541" s="8"/>
@@ -25057,7 +25273,7 @@
       <c r="N545" s="8"/>
       <c r="O545" s="9"/>
     </row>
-    <row r="546" spans="2:15">
+    <row r="546" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B546" s="7"/>
       <c r="C546" s="14"/>
       <c r="D546" s="8"/>
@@ -25073,7 +25289,7 @@
       <c r="N546" s="8"/>
       <c r="O546" s="9"/>
     </row>
-    <row r="547" spans="2:15">
+    <row r="547" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B547" s="7"/>
       <c r="C547" s="14"/>
       <c r="D547" s="8"/>
@@ -25089,7 +25305,7 @@
       <c r="N547" s="8"/>
       <c r="O547" s="9"/>
     </row>
-    <row r="548" spans="2:15">
+    <row r="548" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B548" s="7"/>
       <c r="C548" s="14"/>
       <c r="D548" s="8"/>
@@ -25105,7 +25321,7 @@
       <c r="N548" s="8"/>
       <c r="O548" s="9"/>
     </row>
-    <row r="549" spans="2:15">
+    <row r="549" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B549" s="7"/>
       <c r="C549" s="14"/>
       <c r="D549" s="8"/>
@@ -25121,7 +25337,7 @@
       <c r="N549" s="8"/>
       <c r="O549" s="9"/>
     </row>
-    <row r="550" spans="2:15">
+    <row r="550" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B550" s="7"/>
       <c r="C550" s="14"/>
       <c r="D550" s="8"/>
@@ -25137,7 +25353,7 @@
       <c r="N550" s="8"/>
       <c r="O550" s="9"/>
     </row>
-    <row r="551" spans="2:15">
+    <row r="551" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B551" s="7"/>
       <c r="C551" s="14"/>
       <c r="D551" s="8"/>
@@ -25153,7 +25369,7 @@
       <c r="N551" s="8"/>
       <c r="O551" s="9"/>
     </row>
-    <row r="552" spans="2:15">
+    <row r="552" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B552" s="7"/>
       <c r="C552" s="14"/>
       <c r="D552" s="8"/>
@@ -25169,7 +25385,7 @@
       <c r="N552" s="8"/>
       <c r="O552" s="9"/>
     </row>
-    <row r="553" spans="2:15">
+    <row r="553" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B553" s="7"/>
       <c r="C553" s="14"/>
       <c r="D553" s="8"/>
@@ -25185,7 +25401,7 @@
       <c r="N553" s="8"/>
       <c r="O553" s="9"/>
     </row>
-    <row r="554" spans="2:15">
+    <row r="554" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B554" s="7"/>
       <c r="C554" s="14"/>
       <c r="D554" s="8"/>
@@ -25201,7 +25417,7 @@
       <c r="N554" s="8"/>
       <c r="O554" s="9"/>
     </row>
-    <row r="555" spans="2:15">
+    <row r="555" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B555" s="7"/>
       <c r="C555" s="14"/>
       <c r="D555" s="8"/>
@@ -25217,7 +25433,7 @@
       <c r="N555" s="8"/>
       <c r="O555" s="9"/>
     </row>
-    <row r="556" spans="2:15">
+    <row r="556" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B556" s="7"/>
       <c r="C556" s="14"/>
       <c r="D556" s="8"/>
@@ -25233,7 +25449,7 @@
       <c r="N556" s="8"/>
       <c r="O556" s="9"/>
     </row>
-    <row r="557" spans="2:15">
+    <row r="557" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B557" s="7"/>
       <c r="C557" s="14"/>
       <c r="D557" s="8"/>
@@ -25249,7 +25465,7 @@
       <c r="N557" s="8"/>
       <c r="O557" s="9"/>
     </row>
-    <row r="558" spans="2:15">
+    <row r="558" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B558" s="7"/>
       <c r="C558" s="14"/>
       <c r="D558" s="8"/>
@@ -25265,7 +25481,7 @@
       <c r="N558" s="8"/>
       <c r="O558" s="9"/>
     </row>
-    <row r="559" spans="2:15">
+    <row r="559" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B559" s="7"/>
       <c r="C559" s="14"/>
       <c r="D559" s="8"/>
@@ -25281,7 +25497,7 @@
       <c r="N559" s="8"/>
       <c r="O559" s="9"/>
     </row>
-    <row r="560" spans="2:15">
+    <row r="560" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B560" s="7"/>
       <c r="C560" s="14"/>
       <c r="D560" s="8"/>
@@ -25297,7 +25513,7 @@
       <c r="N560" s="8"/>
       <c r="O560" s="9"/>
     </row>
-    <row r="561" spans="2:15">
+    <row r="561" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B561" s="7"/>
       <c r="C561" s="14"/>
       <c r="D561" s="8"/>
@@ -25313,7 +25529,7 @@
       <c r="N561" s="8"/>
       <c r="O561" s="9"/>
     </row>
-    <row r="562" spans="2:15">
+    <row r="562" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B562" s="7"/>
       <c r="C562" s="14"/>
       <c r="D562" s="8"/>
@@ -25329,7 +25545,7 @@
       <c r="N562" s="8"/>
       <c r="O562" s="9"/>
     </row>
-    <row r="563" spans="2:15">
+    <row r="563" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B563" s="7"/>
       <c r="C563" s="14"/>
       <c r="D563" s="8"/>
@@ -25345,7 +25561,7 @@
       <c r="N563" s="8"/>
       <c r="O563" s="9"/>
     </row>
-    <row r="564" spans="2:15">
+    <row r="564" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B564" s="7"/>
       <c r="C564" s="14"/>
       <c r="D564" s="8"/>
@@ -25361,7 +25577,7 @@
       <c r="N564" s="8"/>
       <c r="O564" s="9"/>
     </row>
-    <row r="565" spans="2:15">
+    <row r="565" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B565" s="7"/>
       <c r="C565" s="14"/>
       <c r="D565" s="8"/>
@@ -25377,7 +25593,7 @@
       <c r="N565" s="8"/>
       <c r="O565" s="9"/>
     </row>
-    <row r="566" spans="2:15">
+    <row r="566" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B566" s="7"/>
       <c r="C566" s="14"/>
       <c r="D566" s="8"/>
@@ -25393,7 +25609,7 @@
       <c r="N566" s="8"/>
       <c r="O566" s="9"/>
     </row>
-    <row r="567" spans="2:15">
+    <row r="567" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B567" s="7"/>
       <c r="C567" s="14"/>
       <c r="D567" s="8"/>
@@ -25409,7 +25625,7 @@
       <c r="N567" s="8"/>
       <c r="O567" s="9"/>
     </row>
-    <row r="568" spans="2:15">
+    <row r="568" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B568" s="7"/>
       <c r="C568" s="14"/>
       <c r="D568" s="8"/>
@@ -25425,7 +25641,7 @@
       <c r="N568" s="8"/>
       <c r="O568" s="9"/>
     </row>
-    <row r="569" spans="2:15">
+    <row r="569" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B569" s="7"/>
       <c r="C569" s="14"/>
       <c r="D569" s="8"/>
@@ -25441,7 +25657,7 @@
       <c r="N569" s="8"/>
       <c r="O569" s="9"/>
     </row>
-    <row r="570" spans="2:15">
+    <row r="570" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B570" s="7"/>
       <c r="C570" s="14"/>
       <c r="D570" s="8"/>
@@ -25457,7 +25673,7 @@
       <c r="N570" s="8"/>
       <c r="O570" s="9"/>
     </row>
-    <row r="571" spans="2:15">
+    <row r="571" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B571" s="7"/>
       <c r="C571" s="14"/>
       <c r="D571" s="8"/>
@@ -25473,7 +25689,7 @@
       <c r="N571" s="8"/>
       <c r="O571" s="9"/>
     </row>
-    <row r="572" spans="2:15">
+    <row r="572" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B572" s="7"/>
       <c r="C572" s="14" t="s">
         <v>79</v>
@@ -25493,7 +25709,7 @@
       <c r="N572" s="8"/>
       <c r="O572" s="9"/>
     </row>
-    <row r="573" spans="2:15">
+    <row r="573" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B573" s="7"/>
       <c r="C573" s="14"/>
       <c r="D573" s="8"/>
@@ -25509,7 +25725,7 @@
       <c r="N573" s="8"/>
       <c r="O573" s="9"/>
     </row>
-    <row r="574" spans="2:15">
+    <row r="574" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B574" s="7"/>
       <c r="C574" s="14" t="s">
         <v>81</v>
@@ -25529,7 +25745,7 @@
       <c r="N574" s="8"/>
       <c r="O574" s="9"/>
     </row>
-    <row r="575" spans="2:15">
+    <row r="575" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B575" s="7"/>
       <c r="C575" s="14"/>
       <c r="D575" s="8"/>
@@ -25545,7 +25761,7 @@
       <c r="N575" s="8"/>
       <c r="O575" s="9"/>
     </row>
-    <row r="576" spans="2:15">
+    <row r="576" spans="2:15" hidden="1" outlineLevel="1">
       <c r="B576" s="7"/>
       <c r="C576" s="14"/>
       <c r="D576" s="8"/>
@@ -25561,7 +25777,7 @@
       <c r="N576" s="8"/>
       <c r="O576" s="9"/>
     </row>
-    <row r="577" spans="2:15">
+    <row r="577" spans="2:15" collapsed="1">
       <c r="B577" s="7"/>
       <c r="C577" s="14"/>
       <c r="D577" s="8"/>
@@ -25579,7 +25795,9 @@
     </row>
     <row r="578" spans="2:15">
       <c r="B578" s="7"/>
-      <c r="C578" s="14"/>
+      <c r="C578" s="14" t="s">
+        <v>83</v>
+      </c>
       <c r="D578" s="8"/>
       <c r="E578" s="8"/>
       <c r="F578" s="8"/>
@@ -25627,7 +25845,9 @@
     </row>
     <row r="581" spans="2:15">
       <c r="B581" s="7"/>
-      <c r="C581" s="14"/>
+      <c r="C581" s="14" t="s">
+        <v>84</v>
+      </c>
       <c r="D581" s="8"/>
       <c r="E581" s="8"/>
       <c r="F581" s="8"/>
@@ -25995,7 +26215,9 @@
     </row>
     <row r="604" spans="2:15">
       <c r="B604" s="7"/>
-      <c r="C604" s="14"/>
+      <c r="C604" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="D604" s="8"/>
       <c r="E604" s="8"/>
       <c r="F604" s="8"/>
@@ -26027,7 +26249,9 @@
     </row>
     <row r="606" spans="2:15">
       <c r="B606" s="7"/>
-      <c r="C606" s="14"/>
+      <c r="C606" s="14" t="s">
+        <v>86</v>
+      </c>
       <c r="D606" s="8"/>
       <c r="E606" s="8"/>
       <c r="F606" s="8"/>
@@ -26059,7 +26283,9 @@
     </row>
     <row r="608" spans="2:15">
       <c r="B608" s="7"/>
-      <c r="C608" s="14"/>
+      <c r="C608" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="D608" s="8"/>
       <c r="E608" s="8"/>
       <c r="F608" s="8"/>
@@ -26091,7 +26317,9 @@
     </row>
     <row r="610" spans="2:15">
       <c r="B610" s="7"/>
-      <c r="C610" s="14"/>
+      <c r="C610" s="14" t="s">
+        <v>88</v>
+      </c>
       <c r="D610" s="8"/>
       <c r="E610" s="8"/>
       <c r="F610" s="8"/>
@@ -26123,7 +26351,9 @@
     </row>
     <row r="612" spans="2:15">
       <c r="B612" s="7"/>
-      <c r="C612" s="14"/>
+      <c r="C612" s="14" t="s">
+        <v>89</v>
+      </c>
       <c r="D612" s="8"/>
       <c r="E612" s="8"/>
       <c r="F612" s="8"/>
